--- a/docs/generated/Парк.xlsx
+++ b/docs/generated/Парк.xlsx
@@ -1287,10 +1287,10 @@
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>1200</v>
@@ -1555,7 +1555,7 @@
         <v>45000</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>approx</t>
+          <t>main</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -4316,13 +4316,13 @@
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>6.46</v>
+        <v>8</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>57.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>approx</t>
+          <t>main</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>10.3</v>
+        <v>16</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>57.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>approx</t>
+          <t>main</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -4368,13 +4368,13 @@
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>13.1</v>
+        <v>25</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>57.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="104">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>approx</t>
+          <t>main</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4394,19 +4394,19 @@
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>15.9</v>
+        <v>30</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>3.05</v>
+        <v>1.8</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>57.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> КБ-403А, КБ-403Б</t>
+          <t xml:space="preserve"> КБ-405-1А, КБ-405-1АМ, КБ-405-2А</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -4420,19 +4420,19 @@
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>18.8</v>
+        <v>7.5</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>2.58</v>
+        <v>8.07</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>57.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> КБ-403А, КБ-403Б</t>
+          <t xml:space="preserve"> КБ-405-1А, КБ-405-1АМ, КБ-405-2А</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -4446,19 +4446,19 @@
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>21.6</v>
+        <v>10.3</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>2.24</v>
+        <v>5.88</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>57.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> КБ-403А, КБ-403Б</t>
+          <t xml:space="preserve"> КБ-405-1А, КБ-405-1АМ, КБ-405-2А</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -4472,19 +4472,19 @@
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>24.4</v>
+        <v>13.1</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>1.99</v>
+        <v>4.62</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>57.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> КБ-403А, КБ-403Б</t>
+          <t xml:space="preserve"> КБ-405-1А, КБ-405-1АМ, КБ-405-2А</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -4498,19 +4498,19 @@
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>27.2</v>
+        <v>15.9</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>1.78</v>
+        <v>3.81</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>57.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> КБ-403А, КБ-403Б</t>
+          <t xml:space="preserve"> КБ-405-1А, КБ-405-1АМ, КБ-405-2А</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -4524,13 +4524,13 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>30</v>
+        <v>18.8</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>1.61</v>
+        <v>3.22</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>57.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="110">
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>7.5</v>
+        <v>21.6</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>8.07</v>
+        <v>2.8</v>
       </c>
       <c r="F110" s="2" t="n">
         <v>70</v>
@@ -4576,10 +4576,10 @@
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>10.3</v>
+        <v>24.4</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>5.88</v>
+        <v>2.48</v>
       </c>
       <c r="F111" s="2" t="n">
         <v>70</v>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>13.1</v>
+        <v>27.2</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>4.62</v>
+        <v>2.23</v>
       </c>
       <c r="F112" s="2" t="n">
         <v>70</v>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>15.9</v>
+        <v>30</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>3.81</v>
+        <v>2.02</v>
       </c>
       <c r="F113" s="2" t="n">
         <v>70</v>
@@ -4640,7 +4640,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> КБ-405-1А, КБ-405-1АМ, КБ-405-2А</t>
+          <t xml:space="preserve"> КБ-408</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -4654,19 +4654,19 @@
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>18.8</v>
+        <v>7.5</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>3.22</v>
+        <v>8.07</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>70</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> КБ-405-1А, КБ-405-1АМ, КБ-405-2А</t>
+          <t xml:space="preserve"> КБ-408</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -4680,19 +4680,19 @@
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>21.6</v>
+        <v>10.3</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>2.8</v>
+        <v>5.88</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>70</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> КБ-405-1А, КБ-405-1АМ, КБ-405-2А</t>
+          <t xml:space="preserve"> КБ-408</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -4706,19 +4706,19 @@
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>24.4</v>
+        <v>13.1</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>2.48</v>
+        <v>4.62</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>70</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> КБ-405-1А, КБ-405-1АМ, КБ-405-2А</t>
+          <t xml:space="preserve"> КБ-408</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -4732,19 +4732,19 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>27.2</v>
+        <v>15.9</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>2.23</v>
+        <v>3.81</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>70</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> КБ-405-1А, КБ-405-1АМ, КБ-405-2А</t>
+          <t xml:space="preserve"> КБ-408</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -4758,13 +4758,13 @@
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>30</v>
+        <v>18.8</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>2.02</v>
+        <v>3.22</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>70</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="119">
@@ -4784,10 +4784,10 @@
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>7.5</v>
+        <v>21.6</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>8.07</v>
+        <v>2.8</v>
       </c>
       <c r="F119" s="2" t="n">
         <v>54.7</v>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>10.3</v>
+        <v>24.4</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>5.88</v>
+        <v>2.48</v>
       </c>
       <c r="F120" s="2" t="n">
         <v>54.7</v>
@@ -4836,10 +4836,10 @@
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>13.1</v>
+        <v>27.2</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>4.62</v>
+        <v>2.23</v>
       </c>
       <c r="F121" s="2" t="n">
         <v>54.7</v>
@@ -4862,142 +4862,12 @@
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>15.9</v>
+        <v>30</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>3.81</v>
+        <v>2.02</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>54.7</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> КБ-408</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>approx</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="E123" s="2" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="F123" s="2" t="n">
-        <v>54.7</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> КБ-408</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>approx</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="E124" s="2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F124" s="2" t="n">
-        <v>54.7</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> КБ-408</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>approx</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E125" s="2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="F125" s="2" t="n">
-        <v>54.7</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> КБ-408</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>approx</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E126" s="2" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>54.7</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> КБ-408</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>approx</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E127" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="F127" s="2" t="n">
         <v>54.7</v>
       </c>
     </row>
